--- a/state/3380_glabbeek_rup.xlsx
+++ b/state/3380_glabbeek_rup.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="21480" yWindow="-1905" windowWidth="21840" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RUP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUP" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -49,7 +49,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,24 @@
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB20B"/>
+        <bgColor rgb="00FFB20B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006E862D"/>
+        <bgColor rgb="006E862D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A38227"/>
+        <bgColor rgb="00A38227"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,6 +206,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="18.42578125" customWidth="1" min="1" max="1"/>
@@ -646,12 +673,12 @@
           <t>gebied voor openluchtrecreatieve verblijven met nabestemming natuur met recreatief medegebruik (vissen)</t>
         </is>
       </c>
-      <c r="S2" s="18" t="inlineStr">
+      <c r="S2" s="21" t="inlineStr">
         <is>
           <t>Zone voor wegenis</t>
         </is>
       </c>
-      <c r="T2" s="18" t="inlineStr">
+      <c r="T2" s="22" t="inlineStr">
         <is>
           <t>Zone voor wonen</t>
         </is>
@@ -661,12 +688,12 @@
           <t>zone voor openlucht recreatieterreinen</t>
         </is>
       </c>
-      <c r="V2" s="18" t="inlineStr">
+      <c r="V2" s="23" t="inlineStr">
         <is>
           <t>Zone voor sporthal en omgeving</t>
         </is>
       </c>
-      <c r="W2" s="18" t="inlineStr">
+      <c r="W2" s="21" t="inlineStr">
         <is>
           <t>Zone voor gemeenschapsvoorzieningen</t>
         </is>
@@ -3861,7 +3888,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A25:A26"/>

--- a/state/3380_glabbeek_rup.xlsx
+++ b/state/3380_glabbeek_rup.xlsx
@@ -653,7 +653,7 @@
           <t>RUP</t>
         </is>
       </c>
-      <c r="O2" s="18" t="inlineStr">
+      <c r="O2" s="21" t="inlineStr">
         <is>
           <t>Zone voor recreatie</t>
         </is>

--- a/state/3380_glabbeek_rup.xlsx
+++ b/state/3380_glabbeek_rup.xlsx
@@ -49,7 +49,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="00A38227"/>
         <bgColor rgb="00A38227"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C4C4C4"/>
+        <bgColor rgb="00C4C4C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FD1807"/>
+        <bgColor rgb="00FD1807"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEBB01"/>
+        <bgColor rgb="00FEBB01"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AFC6EA"/>
+        <bgColor rgb="00AFC6EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -216,6 +240,18 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -223,6 +259,95 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="171450" cy="171450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>16</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="171450" cy="171450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="171450" cy="171450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -673,17 +798,17 @@
           <t>gebied voor openluchtrecreatieve verblijven met nabestemming natuur met recreatief medegebruik (vissen)</t>
         </is>
       </c>
-      <c r="S2" s="21" t="inlineStr">
+      <c r="S2" s="24" t="inlineStr">
         <is>
           <t>Zone voor wegenis</t>
         </is>
       </c>
-      <c r="T2" s="22" t="inlineStr">
+      <c r="T2" s="25" t="inlineStr">
         <is>
           <t>Zone voor wonen</t>
         </is>
       </c>
-      <c r="U2" s="18" t="inlineStr">
+      <c r="U2" s="26" t="inlineStr">
         <is>
           <t>zone voor openlucht recreatieterreinen</t>
         </is>
@@ -693,7 +818,7 @@
           <t>Zone voor sporthal en omgeving</t>
         </is>
       </c>
-      <c r="W2" s="21" t="inlineStr">
+      <c r="W2" s="27" t="inlineStr">
         <is>
           <t>Zone voor gemeenschapsvoorzieningen</t>
         </is>
@@ -3900,5 +4025,6 @@
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>